--- a/tame_output/ON/bt/strategyON_20240313.xlsx
+++ b/tame_output/ON/bt/strategyON_20240313.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-221.1%</t>
+          <t>-221.3%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-85.2%</t>
+          <t>-85.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-54.9%</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-29.7%</t>
         </is>
       </c>
     </row>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-0.5951243457656064</v>
+        <v>-0.5973555628036563</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.910160255161693</v>
+        <v>2.909267768346472</v>
       </c>
       <c r="F1901" t="n">
-        <v>1.692950276843121</v>
+        <v>1.690719059805072</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.164336583887556</v>
+        <v>4.162997853664725</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240313.xlsx
+++ b/tame_output/ON/bt/strategyON_20240313.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>466.1%</t>
+          <t>464.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-221.3%</t>
+          <t>-248.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-85.3%</t>
+          <t>-96.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-54.9%</t>
+          <t>-81.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-45.9%</t>
         </is>
       </c>
     </row>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-0.5973555628036563</v>
+        <v>-0.8661927355361351</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.909267768346472</v>
+        <v>2.801732899253481</v>
       </c>
       <c r="F1901" t="n">
-        <v>1.690719059805072</v>
+        <v>1.421881887072593</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.162997853664725</v>
+        <v>4.001695550025238</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240313.xlsx
+++ b/tame_output/ON/bt/strategyON_20240313.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.529092944932946</v>
+        <v>3.529092944932945</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-0.7039348877502373</v>
+        <v>-0.7040036256327534</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.866002859588597</v>
+        <v>2.865975364435591</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.424384496724264</v>
+        <v>1.42397073162075</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.002563937036998</v>
+        <v>4.00231567797489</v>
       </c>
     </row>
   </sheetData>
